--- a/data/raw/inventory/Week 31/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -3995,7 +3995,7 @@
         <v>16</v>
       </c>
       <c r="F58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G58" t="n">
         <v>5</v>
@@ -4007,7 +4007,7 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K58" t="n">
         <v>16</v>
@@ -4243,7 +4243,7 @@
         <v>9</v>
       </c>
       <c r="F62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K62" t="n">
         <v>9</v>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F85" t="n">
         <v>178</v>
@@ -5681,10 +5681,10 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K85" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L85" t="n">
         <v>1</v>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F119" t="n">
         <v>12</v>
@@ -7789,10 +7789,10 @@
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K119" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -8102,13 +8102,13 @@
         <v>3</v>
       </c>
       <c r="K124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>

--- a/data/raw/inventory/Week 31/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -3003,7 +3003,7 @@
         <v>9</v>
       </c>
       <c r="F42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>9</v>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F63" t="n">
         <v>25</v>
@@ -4317,10 +4317,10 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -5421,7 +5421,7 @@
         <v>96</v>
       </c>
       <c r="F81" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K81" t="n">
         <v>96</v>
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F113" t="n">
         <v>9</v>
@@ -7417,10 +7417,10 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -8084,25 +8084,25 @@
         </is>
       </c>
       <c r="E124" t="n">
+        <v>5</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
         <v>4</v>
       </c>
-      <c r="F124" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" t="n">
-        <v>3</v>
-      </c>
       <c r="K124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -10505,7 +10505,7 @@
         <v>16</v>
       </c>
       <c r="F163" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -10517,7 +10517,7 @@
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K163" t="n">
         <v>17</v>
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F189" t="n">
         <v>27</v>
@@ -12129,10 +12129,10 @@
         <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>

--- a/data/raw/inventory/Week 31/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F18" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1763,19 +1763,19 @@
         <v>9</v>
       </c>
       <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
         <v>9</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>9</v>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -1949,19 +1949,19 @@
         <v>2</v>
       </c>
       <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
         <v>2</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>2</v>
@@ -2011,19 +2011,19 @@
         <v>2</v>
       </c>
       <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>2</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>2</v>
@@ -2259,19 +2259,19 @@
         <v>3</v>
       </c>
       <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
         <v>3</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>3</v>
@@ -2631,7 +2631,7 @@
         <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2643,7 +2643,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
         <v>4</v>
@@ -2693,7 +2693,7 @@
         <v>56</v>
       </c>
       <c r="F37" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2705,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>56</v>
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2891,10 +2891,10 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>7</v>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2953,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K41" t="n">
         <v>7</v>
@@ -3003,19 +3003,19 @@
         <v>9</v>
       </c>
       <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
         <v>9</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>9</v>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F45" t="n">
         <v>5</v>
@@ -3201,10 +3201,10 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F46" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3313,7 +3313,7 @@
         <v>21</v>
       </c>
       <c r="F47" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>21</v>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F48" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -3387,13 +3387,13 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>9</v>
       </c>
       <c r="F49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>9</v>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F50" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G50" t="n">
         <v>20</v>
@@ -3514,7 +3514,7 @@
         <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -3685,7 +3685,7 @@
         <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
         <v>4</v>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>6</v>
@@ -3883,10 +3883,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F58" t="n">
         <v>9</v>
@@ -4007,10 +4007,10 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
         <v>20</v>
       </c>
       <c r="F59" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
         <v>20</v>
@@ -4181,7 +4181,7 @@
         <v>19</v>
       </c>
       <c r="F61" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
         <v>19</v>
@@ -4243,7 +4243,7 @@
         <v>9</v>
       </c>
       <c r="F62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
         <v>9</v>
@@ -4305,7 +4305,7 @@
         <v>26</v>
       </c>
       <c r="F63" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>26</v>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F67" t="n">
         <v>4</v>
@@ -4565,10 +4565,10 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -4751,10 +4751,10 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F81" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -5433,10 +5433,10 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K81" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -5480,10 +5480,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F82" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -5498,7 +5498,7 @@
         <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L82" t="n">
         <v>1</v>
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -5619,10 +5619,10 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>180</v>
       </c>
       <c r="F85" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -5681,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K85" t="n">
         <v>181</v>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -5805,10 +5805,10 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="K87" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -5867,10 +5867,10 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F103" t="n">
         <v>3</v>
@@ -6797,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F104" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K104" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F105" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -6921,10 +6921,10 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K105" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L105" t="n">
         <v>1</v>
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F108" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -7110,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F112" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -7355,10 +7355,10 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K112" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -7591,7 +7591,7 @@
         <v>3</v>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K116" t="n">
         <v>3</v>
@@ -7712,10 +7712,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -7730,7 +7730,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L118" t="n">
         <v>1</v>
@@ -7774,10 +7774,10 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F119" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -7789,10 +7789,10 @@
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -8099,10 +8099,10 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K124" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F125" t="n">
         <v>79</v>
@@ -8161,10 +8161,10 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K125" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -8518,10 +8518,10 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F131" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -8533,10 +8533,10 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -8580,10 +8580,10 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F132" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G132" t="n">
         <v>12</v>
@@ -8595,10 +8595,10 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L132" t="n">
         <v>1</v>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F140" t="n">
         <v>2</v>
@@ -9091,10 +9091,10 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -9634,10 +9634,10 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F149" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -9652,7 +9652,7 @@
         <v>1</v>
       </c>
       <c r="K149" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -10319,7 +10319,7 @@
         <v>2</v>
       </c>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -10331,7 +10331,7 @@
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K160" t="n">
         <v>2</v>
@@ -10378,10 +10378,10 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F161" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -10396,7 +10396,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -10440,10 +10440,10 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F162" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G162" t="n">
         <v>5</v>
@@ -10458,7 +10458,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -11742,7 +11742,7 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F183" t="n">
         <v>35</v>
@@ -11757,10 +11757,10 @@
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K183" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -12114,10 +12114,10 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F189" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -12129,10 +12129,10 @@
         <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K189" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -12486,7 +12486,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F195" t="n">
         <v>1</v>
@@ -12501,10 +12501,10 @@
         <v>0</v>
       </c>
       <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
         <v>1</v>
-      </c>
-      <c r="K195" t="n">
-        <v>2</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -12858,7 +12858,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F201" t="n">
         <v>0</v>
@@ -12873,10 +12873,10 @@
         <v>0</v>
       </c>
       <c r="J201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -13233,19 +13233,19 @@
         <v>1</v>
       </c>
       <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
         <v>1</v>
-      </c>
-      <c r="G207" t="n">
-        <v>0</v>
-      </c>
-      <c r="H207" t="n">
-        <v>0</v>
-      </c>
-      <c r="I207" t="n">
-        <v>0</v>
-      </c>
-      <c r="J207" t="n">
-        <v>0</v>
       </c>
       <c r="K207" t="n">
         <v>1</v>

--- a/data/raw/inventory/Week 31/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -1391,7 +1391,7 @@
         <v>46</v>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>46</v>
@@ -1515,7 +1515,7 @@
         <v>44</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>44</v>
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F72" t="n">
         <v>18</v>
@@ -4875,10 +4875,10 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F82" t="n">
         <v>73</v>
@@ -5495,10 +5495,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L82" t="n">
         <v>1</v>
@@ -6844,7 +6844,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F104" t="n">
         <v>96</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K104" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F119" t="n">
         <v>13</v>
@@ -7789,10 +7789,10 @@
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -9079,7 +9079,7 @@
         <v>2</v>
       </c>
       <c r="F140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -9091,7 +9091,7 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K140" t="n">
         <v>2</v>
